--- a/VerveStacks_NGA_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_NGA_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18189321-614D-4656-8F64-1F4614DAC804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2AA7AB9-2E67-4A7C-AD6F-0522663166D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -996,24 +996,144 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_NGA_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NGA_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NGA_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NGA_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NGA_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NGA_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NGA_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NGA_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NGA_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NGA_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NGA_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NGA_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NGA_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_NGA_005</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 5</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_NGA_015</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 15</t>
   </si>
   <si>
+    <t>distr_solelc_spv_NGA_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NGA_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NGA_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NGA_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NGA_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NGA_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NGA_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_NGA_033</t>
   </si>
   <si>
@@ -1038,34 +1158,40 @@
     <t>connecting solar to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_solelc_spv_NGA_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NGA_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NGA_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NGA_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NGA_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
+    <t>distr_solelc_spv_NGA_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NGA_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NGA_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NGA_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NGA_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NGA_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
   </si>
   <si>
     <t>distr_solelc_spv_NGA_004</t>
@@ -1092,166 +1218,94 @@
     <t>connecting solar to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_solelc_spv_NGA_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NGA_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NGA_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NGA_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NGA_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NGA_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NGA_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NGA_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NGA_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NGA_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NGA_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NGA_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NGA_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NGA_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NGA_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NGA_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NGA_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NGA_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NGA_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NGA_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NGA_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w215459565-330_NGA,e_w556550171-330_NGA,e_NG12-330_NGA</t>
+  </si>
+  <si>
+    <t>e_w266712817-330_NGA,e_w563723584-330_NGA</t>
+  </si>
+  <si>
+    <t>e_w556550171-330_NGA,e_NG12-330_NGA,e_w266617120-330_NGA</t>
+  </si>
+  <si>
+    <t>e_w477596994-330_NGA,e_w481286430-330_NGA</t>
+  </si>
+  <si>
+    <t>e_w477596994-330_NGA</t>
+  </si>
+  <si>
+    <t>e_w481286430-330_NGA,e_w564410486-330_NGA,e_w556550171-330_NGA,e_w39469643-330_NGA</t>
+  </si>
+  <si>
+    <t>e_w477596994-330_NGA,e_w215459565-330_NGA,e_w556550171-330_NGA</t>
+  </si>
+  <si>
+    <t>e_w564462599-330_NGA,e_w671893504-330_NGA,e_w215459565-330_NGA,e_NG12-330_NGA</t>
+  </si>
+  <si>
     <t>e_w564462599-330_NGA</t>
   </si>
   <si>
+    <t>e_w215459565-330_NGA,e_NG12-330_NGA</t>
+  </si>
+  <si>
     <t>e_w266712817-330_NGA</t>
   </si>
   <si>
+    <t>e_w564462599-330_NGA,e_w671893504-330_NGA</t>
+  </si>
+  <si>
+    <t>e_NG12-330_NGA,e_w266712817-330_NGA</t>
+  </si>
+  <si>
+    <t>e_NG1-330_NGA</t>
+  </si>
+  <si>
+    <t>e_NG9-330_NGA,e_w477596994-330_NGA,e_w564462599-330_NGA,e_w215459565-330_NGA</t>
+  </si>
+  <si>
+    <t>e_w564410486-330_NGA,e_NG1-330_NGA</t>
+  </si>
+  <si>
+    <t>e_w334825256-330_NGA,e_NG12-330_NGA</t>
+  </si>
+  <si>
+    <t>e_w266617120-330_NGA,e_NG1-330_NGA,e_w266712817-330_NGA,e_w563723584-330_NGA</t>
+  </si>
+  <si>
+    <t>e_NG1-330_NGA,e_w563723584-330_NGA</t>
+  </si>
+  <si>
+    <t>e_w334825256-330_NGA</t>
+  </si>
+  <si>
     <t>e_w556550171-330_NGA,e_w39469643-330_NGA,e_w266617120-330_NGA</t>
   </si>
   <si>
-    <t>e_w334825256-330_NGA</t>
-  </si>
-  <si>
     <t>e_NG12-330_NGA</t>
   </si>
   <si>
     <t>e_NG12-330_NGA,e_w266617120-330_NGA,e_w266712817-330_NGA</t>
   </si>
   <si>
-    <t>e_w556550171-330_NGA,e_NG12-330_NGA,e_w266617120-330_NGA</t>
-  </si>
-  <si>
-    <t>e_NG1-330_NGA,e_w563723584-330_NGA</t>
-  </si>
-  <si>
-    <t>e_w564462599-330_NGA,e_w671893504-330_NGA</t>
-  </si>
-  <si>
-    <t>e_NG12-330_NGA,e_w266712817-330_NGA</t>
+    <t>e_NG9-330_NGA,e_w477596994-330_NGA</t>
+  </si>
+  <si>
+    <t>e_w481286430-330_NGA</t>
+  </si>
+  <si>
+    <t>e_w564410486-330_NGA,e_w481286430-330_NGA,e_w39469643-330_NGA,e_NG1-330_NGA</t>
+  </si>
+  <si>
+    <t>e_w564462599-330_NGA,e_w334825256-330_NGA</t>
+  </si>
+  <si>
+    <t>e_NG12-330_NGA,e_w334825256-330_NGA</t>
   </si>
   <si>
     <t>e_NG9-330_NGA,e_w564462599-330_NGA</t>
@@ -1263,60 +1317,6 @@
     <t>e_w563723584-330_NGA</t>
   </si>
   <si>
-    <t>e_w477596994-330_NGA,e_w481286430-330_NGA</t>
-  </si>
-  <si>
-    <t>e_w477596994-330_NGA</t>
-  </si>
-  <si>
-    <t>e_w481286430-330_NGA,e_w564410486-330_NGA,e_w556550171-330_NGA,e_w39469643-330_NGA</t>
-  </si>
-  <si>
-    <t>e_NG9-330_NGA,e_w477596994-330_NGA,e_w564462599-330_NGA,e_w215459565-330_NGA</t>
-  </si>
-  <si>
-    <t>e_w564410486-330_NGA,e_NG1-330_NGA</t>
-  </si>
-  <si>
-    <t>e_w334825256-330_NGA,e_NG12-330_NGA</t>
-  </si>
-  <si>
-    <t>e_w266617120-330_NGA,e_NG1-330_NGA,e_w266712817-330_NGA,e_w563723584-330_NGA</t>
-  </si>
-  <si>
-    <t>e_NG9-330_NGA,e_w477596994-330_NGA</t>
-  </si>
-  <si>
-    <t>e_w481286430-330_NGA</t>
-  </si>
-  <si>
-    <t>e_w564410486-330_NGA,e_w481286430-330_NGA,e_w39469643-330_NGA,e_NG1-330_NGA</t>
-  </si>
-  <si>
-    <t>e_w564462599-330_NGA,e_w334825256-330_NGA</t>
-  </si>
-  <si>
-    <t>e_NG12-330_NGA,e_w334825256-330_NGA</t>
-  </si>
-  <si>
-    <t>e_NG1-330_NGA</t>
-  </si>
-  <si>
-    <t>e_w477596994-330_NGA,e_w215459565-330_NGA,e_w556550171-330_NGA</t>
-  </si>
-  <si>
-    <t>e_w564462599-330_NGA,e_w671893504-330_NGA,e_w215459565-330_NGA,e_NG12-330_NGA</t>
-  </si>
-  <si>
-    <t>e_w215459565-330_NGA,e_NG12-330_NGA</t>
-  </si>
-  <si>
-    <t>e_w215459565-330_NGA,e_w556550171-330_NGA,e_NG12-330_NGA</t>
-  </si>
-  <si>
-    <t>e_w266712817-330_NGA,e_w563723584-330_NGA</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_NGA_015</t>
   </si>
   <si>
@@ -1335,6 +1335,90 @@
     <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
+    <t>distr_wonelc_won_NGA_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NGA_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NGA_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NGA_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NGA_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NGA_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NGA_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NGA_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NGA_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NGA_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NGA_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NGA_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NGA_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NGA_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_NGA_009</t>
   </si>
   <si>
@@ -1353,28 +1437,22 @@
     <t>connecting wind onshore to buses in cluster 21</t>
   </si>
   <si>
-    <t>distr_wonelc_won_NGA_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NGA_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NGA_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NGA_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
+    <t>distr_wonelc_won_NGA_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NGA_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NGA_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
   </si>
   <si>
     <t>distr_wonelc_won_NGA_024</t>
@@ -1383,30 +1461,6 @@
     <t>connecting wind onshore to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_wonelc_won_NGA_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NGA_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NGA_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NGA_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_NGA_014</t>
   </si>
   <si>
@@ -1425,60 +1479,6 @@
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wonelc_won_NGA_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NGA_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NGA_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NGA_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NGA_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NGA_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NGA_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NGA_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NGA_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
     <t>elc_won_NGA_015</t>
   </si>
   <si>
@@ -1491,6 +1491,69 @@
     <t>elc_won_NGA_002</t>
   </si>
   <si>
+    <t>elc_won_NGA_008</t>
+  </si>
+  <si>
+    <t>e_NG9-330_NGA</t>
+  </si>
+  <si>
+    <t>elc_won_NGA_013</t>
+  </si>
+  <si>
+    <t>e_w564410486-330_NGA,e_w39469643-330_NGA,e_NG1-330_NGA</t>
+  </si>
+  <si>
+    <t>elc_won_NGA_020</t>
+  </si>
+  <si>
+    <t>e_NG1-330_NGA,e_w266712817-330_NGA,e_w563723584-330_NGA</t>
+  </si>
+  <si>
+    <t>elc_won_NGA_018</t>
+  </si>
+  <si>
+    <t>elc_won_NGA_010</t>
+  </si>
+  <si>
+    <t>elc_won_NGA_022</t>
+  </si>
+  <si>
+    <t>elc_won_NGA_004</t>
+  </si>
+  <si>
+    <t>elc_won_NGA_006</t>
+  </si>
+  <si>
+    <t>e_w481286430-330_NGA,e_w477596994-330_NGA</t>
+  </si>
+  <si>
+    <t>elc_won_NGA_011</t>
+  </si>
+  <si>
+    <t>e_w481286430-330_NGA,e_w564410486-330_NGA</t>
+  </si>
+  <si>
+    <t>elc_won_NGA_017</t>
+  </si>
+  <si>
+    <t>elc_won_NGA_007</t>
+  </si>
+  <si>
+    <t>e_w477596994-330_NGA,e_w481286430-330_NGA,e_w215459565-330_NGA</t>
+  </si>
+  <si>
+    <t>elc_won_NGA_019</t>
+  </si>
+  <si>
+    <t>elc_won_NGA_026</t>
+  </si>
+  <si>
+    <t>elc_won_NGA_025</t>
+  </si>
+  <si>
+    <t>e_NG1-330_NGA,e_w266617120-330_NGA</t>
+  </si>
+  <si>
     <t>elc_won_NGA_009</t>
   </si>
   <si>
@@ -1506,19 +1569,16 @@
     <t>elc_won_NGA_021</t>
   </si>
   <si>
-    <t>elc_won_NGA_025</t>
-  </si>
-  <si>
-    <t>e_NG1-330_NGA,e_w266617120-330_NGA</t>
-  </si>
-  <si>
-    <t>elc_won_NGA_010</t>
-  </si>
-  <si>
-    <t>elc_won_NGA_022</t>
-  </si>
-  <si>
-    <t>elc_won_NGA_004</t>
+    <t>elc_won_NGA_003</t>
+  </si>
+  <si>
+    <t>elc_won_NGA_012</t>
+  </si>
+  <si>
+    <t>e_w564410486-330_NGA,e_w481286430-330_NGA</t>
+  </si>
+  <si>
+    <t>elc_won_NGA_016</t>
   </si>
   <si>
     <t>elc_won_NGA_024</t>
@@ -1527,27 +1587,6 @@
     <t>e_w266617120-330_NGA,e_NG1-330_NGA</t>
   </si>
   <si>
-    <t>elc_won_NGA_008</t>
-  </si>
-  <si>
-    <t>e_NG9-330_NGA</t>
-  </si>
-  <si>
-    <t>elc_won_NGA_013</t>
-  </si>
-  <si>
-    <t>e_w564410486-330_NGA,e_w39469643-330_NGA,e_NG1-330_NGA</t>
-  </si>
-  <si>
-    <t>elc_won_NGA_020</t>
-  </si>
-  <si>
-    <t>e_NG1-330_NGA,e_w266712817-330_NGA,e_w563723584-330_NGA</t>
-  </si>
-  <si>
-    <t>elc_won_NGA_018</t>
-  </si>
-  <si>
     <t>elc_won_NGA_014</t>
   </si>
   <si>
@@ -1560,45 +1599,6 @@
     <t>e_NG12-330_NGA,e_w215459565-330_NGA</t>
   </si>
   <si>
-    <t>elc_won_NGA_007</t>
-  </si>
-  <si>
-    <t>e_w477596994-330_NGA,e_w481286430-330_NGA,e_w215459565-330_NGA</t>
-  </si>
-  <si>
-    <t>elc_won_NGA_003</t>
-  </si>
-  <si>
-    <t>elc_won_NGA_019</t>
-  </si>
-  <si>
-    <t>elc_won_NGA_026</t>
-  </si>
-  <si>
-    <t>elc_won_NGA_006</t>
-  </si>
-  <si>
-    <t>e_w481286430-330_NGA,e_w477596994-330_NGA</t>
-  </si>
-  <si>
-    <t>elc_won_NGA_011</t>
-  </si>
-  <si>
-    <t>e_w481286430-330_NGA,e_w564410486-330_NGA</t>
-  </si>
-  <si>
-    <t>elc_won_NGA_017</t>
-  </si>
-  <si>
-    <t>elc_won_NGA_012</t>
-  </si>
-  <si>
-    <t>e_w564410486-330_NGA,e_w481286430-330_NGA</t>
-  </si>
-  <si>
-    <t>elc_won_NGA_016</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_NGA_006</t>
   </si>
   <si>
@@ -1611,6 +1611,24 @@
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_NGA_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NGA_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NGA_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_NGA_010</t>
   </si>
   <si>
@@ -1629,42 +1647,36 @@
     <t>connecting wind offshore to buses in cluster 8</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_NGA_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_NGA_003</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_NGA_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NGA_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NGA_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NGA_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
     <t>elc_wof_NGA_006</t>
   </si>
   <si>
     <t>elc_wof_NGA_009</t>
   </si>
   <si>
+    <t>elc_wof_NGA_002</t>
+  </si>
+  <si>
+    <t>elc_wof_NGA_004</t>
+  </si>
+  <si>
+    <t>e_w564462599-330_NGA,e_NG9-330_NGA</t>
+  </si>
+  <si>
+    <t>elc_wof_NGA_005</t>
+  </si>
+  <si>
     <t>elc_wof_NGA_010</t>
   </si>
   <si>
@@ -1674,22 +1686,10 @@
     <t>elc_wof_NGA_008</t>
   </si>
   <si>
+    <t>elc_wof_NGA_007</t>
+  </si>
+  <si>
     <t>elc_wof_NGA_003</t>
-  </si>
-  <si>
-    <t>elc_wof_NGA_005</t>
-  </si>
-  <si>
-    <t>elc_wof_NGA_007</t>
-  </si>
-  <si>
-    <t>elc_wof_NGA_002</t>
-  </si>
-  <si>
-    <t>elc_wof_NGA_004</t>
-  </si>
-  <si>
-    <t>e_w564462599-330_NGA,e_NG9-330_NGA</t>
   </si>
   <si>
     <t>e_won_NGA_001</t>
@@ -6739,7 +6739,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4594E9BE-4282-4BC8-9FA4-793C584C10AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAF8EACD-600E-4D69-A920-AE550C0CB690}">
   <dimension ref="B9:BD46"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6977,16 +6977,16 @@
         <v>289</v>
       </c>
       <c r="Y11" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="Z11" t="s">
         <v>365</v>
       </c>
       <c r="AA11">
-        <v>0.99832768028365393</v>
+        <v>0.99489048613238573</v>
       </c>
       <c r="AB11">
-        <v>30.659194799678048</v>
+        <v>93.674420906261602</v>
       </c>
       <c r="AD11" t="s">
         <v>288</v>
@@ -7052,7 +7052,7 @@
         <v>510</v>
       </c>
       <c r="BB11" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="BC11">
         <v>0.99132158137897763</v>
@@ -7123,16 +7123,16 @@
         <v>293</v>
       </c>
       <c r="Y12" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Z12" t="s">
         <v>366</v>
       </c>
       <c r="AA12">
-        <v>0.98416398409272543</v>
+        <v>0.99436579068013853</v>
       </c>
       <c r="AB12">
-        <v>290.32695830003399</v>
+        <v>103.29383753079337</v>
       </c>
       <c r="AD12" t="s">
         <v>288</v>
@@ -7162,7 +7162,7 @@
         <v>452</v>
       </c>
       <c r="AN12" t="s">
-        <v>370</v>
+        <v>387</v>
       </c>
       <c r="AO12">
         <v>0.99069345154297106</v>
@@ -7198,7 +7198,7 @@
         <v>511</v>
       </c>
       <c r="BB12" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="BC12">
         <v>0.99755731205629283</v>
@@ -7269,16 +7269,16 @@
         <v>295</v>
       </c>
       <c r="Y13" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="Z13" t="s">
         <v>367</v>
       </c>
       <c r="AA13">
-        <v>0.99642867204968677</v>
+        <v>0.9940266623681554</v>
       </c>
       <c r="AB13">
-        <v>65.474345755743457</v>
+        <v>109.51118991715018</v>
       </c>
       <c r="AD13" t="s">
         <v>288</v>
@@ -7308,7 +7308,7 @@
         <v>453</v>
       </c>
       <c r="AN13" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="AO13">
         <v>0.99537626424805781</v>
@@ -7344,13 +7344,13 @@
         <v>512</v>
       </c>
       <c r="BB13" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="BC13">
-        <v>0.99371472191320109</v>
+        <v>0.9962053430710629</v>
       </c>
       <c r="BD13">
-        <v>115.23009825798009</v>
+        <v>69.568710363846861</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7415,16 +7415,16 @@
         <v>297</v>
       </c>
       <c r="Y14" t="s">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="Z14" t="s">
         <v>368</v>
       </c>
       <c r="AA14">
-        <v>0.99882431199806432</v>
+        <v>0.996629171401053</v>
       </c>
       <c r="AB14">
-        <v>21.554280035486567</v>
+        <v>61.798524314027716</v>
       </c>
       <c r="AD14" t="s">
         <v>288</v>
@@ -7457,10 +7457,10 @@
         <v>455</v>
       </c>
       <c r="AO14">
-        <v>0.9964390810242717</v>
+        <v>0.99795762496221851</v>
       </c>
       <c r="AP14">
-        <v>65.283514555019096</v>
+        <v>37.443542359327118</v>
       </c>
       <c r="AR14" t="s">
         <v>288</v>
@@ -7490,13 +7490,13 @@
         <v>513</v>
       </c>
       <c r="BB14" t="s">
-        <v>375</v>
+        <v>514</v>
       </c>
       <c r="BC14">
-        <v>0.99794494286432878</v>
+        <v>0.99246115999793105</v>
       </c>
       <c r="BD14">
-        <v>37.67604748730637</v>
+        <v>138.21206670459694</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7561,16 +7561,16 @@
         <v>299</v>
       </c>
       <c r="Y15" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="Z15" t="s">
         <v>369</v>
       </c>
       <c r="AA15">
-        <v>0.99629642371863703</v>
+        <v>0.99723470592138874</v>
       </c>
       <c r="AB15">
-        <v>67.898898491655515</v>
+        <v>50.697058107873339</v>
       </c>
       <c r="AD15" t="s">
         <v>288</v>
@@ -7603,10 +7603,10 @@
         <v>457</v>
       </c>
       <c r="AO15">
-        <v>0.99534990870245532</v>
+        <v>0.99207403494667001</v>
       </c>
       <c r="AP15">
-        <v>85.251673788320105</v>
+        <v>145.30935931104892</v>
       </c>
       <c r="AR15" t="s">
         <v>288</v>
@@ -7633,16 +7633,16 @@
         <v>498</v>
       </c>
       <c r="BA15" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="BB15" t="s">
-        <v>368</v>
+        <v>391</v>
       </c>
       <c r="BC15">
-        <v>0.99337755486839363</v>
+        <v>0.9888409065104441</v>
       </c>
       <c r="BD15">
-        <v>121.41149407945062</v>
+        <v>204.58338064185853</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7707,16 +7707,16 @@
         <v>301</v>
       </c>
       <c r="Y16" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="Z16" t="s">
         <v>370</v>
       </c>
       <c r="AA16">
-        <v>0.99095032933880767</v>
+        <v>0.99339354842512728</v>
       </c>
       <c r="AB16">
-        <v>165.91062878852651</v>
+        <v>121.1182788726671</v>
       </c>
       <c r="AD16" t="s">
         <v>288</v>
@@ -7746,13 +7746,13 @@
         <v>458</v>
       </c>
       <c r="AN16" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AO16">
-        <v>0.99555964959117016</v>
+        <v>0.99152317643653909</v>
       </c>
       <c r="AP16">
-        <v>81.406424161880452</v>
+        <v>155.40843199678267</v>
       </c>
       <c r="AR16" t="s">
         <v>288</v>
@@ -7779,16 +7779,16 @@
         <v>500</v>
       </c>
       <c r="BA16" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="BB16" t="s">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="BC16">
-        <v>0.99174031680019514</v>
+        <v>0.99371472191320109</v>
       </c>
       <c r="BD16">
-        <v>151.42752532975524</v>
+        <v>115.23009825798009</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7853,16 +7853,16 @@
         <v>303</v>
       </c>
       <c r="Y17" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="Z17" t="s">
         <v>371</v>
       </c>
       <c r="AA17">
-        <v>0.9940266623681554</v>
+        <v>0.9963457067026108</v>
       </c>
       <c r="AB17">
-        <v>109.51118991715018</v>
+        <v>66.99537711880258</v>
       </c>
       <c r="AD17" t="s">
         <v>288</v>
@@ -7889,16 +7889,16 @@
         <v>408</v>
       </c>
       <c r="AM17" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN17" t="s">
-        <v>460</v>
+        <v>383</v>
       </c>
       <c r="AO17">
-        <v>0.99637613831578808</v>
+        <v>0.98839759805196303</v>
       </c>
       <c r="AP17">
-        <v>66.437464210551497</v>
+        <v>212.71070238067816</v>
       </c>
       <c r="AR17" t="s">
         <v>288</v>
@@ -7925,16 +7925,16 @@
         <v>502</v>
       </c>
       <c r="BA17" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="BB17" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="BC17">
-        <v>0.9888409065104441</v>
+        <v>0.99794494286432878</v>
       </c>
       <c r="BD17">
-        <v>204.58338064185853</v>
+        <v>37.67604748730637</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7999,16 +7999,16 @@
         <v>305</v>
       </c>
       <c r="Y18" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Z18" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="AA18">
-        <v>0.99750455285561002</v>
+        <v>0.99728758220200375</v>
       </c>
       <c r="AB18">
-        <v>45.749864313816033</v>
+        <v>49.727659629930621</v>
       </c>
       <c r="AD18" t="s">
         <v>288</v>
@@ -8038,7 +8038,7 @@
         <v>461</v>
       </c>
       <c r="AN18" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="AO18">
         <v>0.9938298282896767</v>
@@ -8071,16 +8071,16 @@
         <v>504</v>
       </c>
       <c r="BA18" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="BB18" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="BC18">
-        <v>0.99268778174342398</v>
+        <v>0.99337755486839363</v>
       </c>
       <c r="BD18">
-        <v>134.05733470389279</v>
+        <v>121.41149407945062</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8145,16 +8145,16 @@
         <v>307</v>
       </c>
       <c r="Y19" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="Z19" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AA19">
-        <v>0.99167897814293215</v>
+        <v>0.99744993905722468</v>
       </c>
       <c r="AB19">
-        <v>152.55206737957732</v>
+        <v>46.751117284213812</v>
       </c>
       <c r="AD19" t="s">
         <v>288</v>
@@ -8184,7 +8184,7 @@
         <v>462</v>
       </c>
       <c r="AN19" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="AO19">
         <v>0.99592480739127276</v>
@@ -8217,16 +8217,16 @@
         <v>506</v>
       </c>
       <c r="BA19" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="BB19" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="BC19">
-        <v>0.9962053430710629</v>
+        <v>0.99268778174342398</v>
       </c>
       <c r="BD19">
-        <v>69.568710363846861</v>
+        <v>134.05733470389279</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8291,16 +8291,16 @@
         <v>309</v>
       </c>
       <c r="Y20" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="Z20" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AA20">
-        <v>0.99805028151894915</v>
+        <v>0.99655017109874156</v>
       </c>
       <c r="AB20">
-        <v>35.744838819266263</v>
+        <v>63.246863189739024</v>
       </c>
       <c r="AD20" t="s">
         <v>288</v>
@@ -8330,7 +8330,7 @@
         <v>463</v>
       </c>
       <c r="AN20" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="AO20">
         <v>0.99354454384798807</v>
@@ -8363,16 +8363,16 @@
         <v>508</v>
       </c>
       <c r="BA20" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="BB20" t="s">
-        <v>520</v>
+        <v>373</v>
       </c>
       <c r="BC20">
-        <v>0.99246115999793105</v>
+        <v>0.99174031680019514</v>
       </c>
       <c r="BD20">
-        <v>138.21206670459694</v>
+        <v>151.42752532975524</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8437,16 +8437,16 @@
         <v>311</v>
       </c>
       <c r="Y21" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="Z21" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AA21">
-        <v>0.98395338050941106</v>
+        <v>0.99589467345586935</v>
       </c>
       <c r="AB21">
-        <v>294.18802399413073</v>
+        <v>75.264319975727958</v>
       </c>
       <c r="AD21" t="s">
         <v>288</v>
@@ -8479,10 +8479,10 @@
         <v>465</v>
       </c>
       <c r="AO21">
-        <v>0.99501745221162918</v>
+        <v>0.99429686126958916</v>
       </c>
       <c r="AP21">
-        <v>91.346709453464783</v>
+        <v>104.55754339086491</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8547,16 +8547,16 @@
         <v>313</v>
       </c>
       <c r="Y22" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="Z22" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AA22">
-        <v>0.99802177249546054</v>
+        <v>0.99805028151894915</v>
       </c>
       <c r="AB22">
-        <v>36.267504249889917</v>
+        <v>35.744838819266263</v>
       </c>
       <c r="AD22" t="s">
         <v>288</v>
@@ -8589,10 +8589,10 @@
         <v>467</v>
       </c>
       <c r="AO22">
-        <v>0.99795762496221851</v>
+        <v>0.99178855761800622</v>
       </c>
       <c r="AP22">
-        <v>37.443542359327118</v>
+        <v>150.54311033655213</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8657,16 +8657,16 @@
         <v>315</v>
       </c>
       <c r="Y23" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="Z23" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA23">
-        <v>0.99769464806112851</v>
+        <v>0.98395338050941106</v>
       </c>
       <c r="AB23">
-        <v>42.264785545976984</v>
+        <v>294.18802399413073</v>
       </c>
       <c r="AD23" t="s">
         <v>288</v>
@@ -8696,13 +8696,13 @@
         <v>468</v>
       </c>
       <c r="AN23" t="s">
-        <v>469</v>
+        <v>366</v>
       </c>
       <c r="AO23">
-        <v>0.99207403494667001</v>
+        <v>0.99475386493829931</v>
       </c>
       <c r="AP23">
-        <v>145.30935931104892</v>
+        <v>96.179142797845941</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8767,16 +8767,16 @@
         <v>317</v>
       </c>
       <c r="Y24" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="Z24" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="AA24">
-        <v>0.99605704806429607</v>
+        <v>0.99832768028365393</v>
       </c>
       <c r="AB24">
-        <v>72.28745215457208</v>
+        <v>30.659194799678048</v>
       </c>
       <c r="AD24" t="s">
         <v>288</v>
@@ -8803,16 +8803,16 @@
         <v>422</v>
       </c>
       <c r="AM24" t="s">
+        <v>469</v>
+      </c>
+      <c r="AN24" t="s">
         <v>470</v>
       </c>
-      <c r="AN24" t="s">
-        <v>471</v>
-      </c>
       <c r="AO24">
-        <v>0.99152317643653909</v>
+        <v>0.99740664776461363</v>
       </c>
       <c r="AP24">
-        <v>155.40843199678267</v>
+        <v>47.544790982083583</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8877,16 +8877,16 @@
         <v>319</v>
       </c>
       <c r="Y25" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="Z25" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AA25">
-        <v>0.99262439568706373</v>
+        <v>0.98416398409272543</v>
       </c>
       <c r="AB25">
-        <v>135.21941240383219</v>
+        <v>290.32695830003399</v>
       </c>
       <c r="AD25" t="s">
         <v>288</v>
@@ -8913,16 +8913,16 @@
         <v>424</v>
       </c>
       <c r="AM25" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AN25" t="s">
-        <v>372</v>
+        <v>395</v>
       </c>
       <c r="AO25">
-        <v>0.98839759805196303</v>
+        <v>0.99008544123370779</v>
       </c>
       <c r="AP25">
-        <v>212.71070238067816</v>
+        <v>181.76691071535706</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8987,16 +8987,16 @@
         <v>321</v>
       </c>
       <c r="Y26" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="Z26" t="s">
         <v>378</v>
       </c>
       <c r="AA26">
-        <v>0.996629171401053</v>
+        <v>0.99644500818542014</v>
       </c>
       <c r="AB26">
-        <v>61.798524314027716</v>
+        <v>65.174849933963586</v>
       </c>
       <c r="AD26" t="s">
         <v>288</v>
@@ -9023,16 +9023,16 @@
         <v>426</v>
       </c>
       <c r="AM26" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AN26" t="s">
-        <v>451</v>
+        <v>366</v>
       </c>
       <c r="AO26">
-        <v>0.99582871194680656</v>
+        <v>0.99283555585293171</v>
       </c>
       <c r="AP26">
-        <v>76.473614308545862</v>
+        <v>131.34814269625272</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9097,16 +9097,16 @@
         <v>323</v>
       </c>
       <c r="Y27" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Z27" t="s">
         <v>379</v>
       </c>
       <c r="AA27">
-        <v>0.99723470592138874</v>
+        <v>0.99732710525923551</v>
       </c>
       <c r="AB27">
-        <v>50.697058107873339</v>
+        <v>49.003070247349498</v>
       </c>
       <c r="AD27" t="s">
         <v>288</v>
@@ -9133,16 +9133,16 @@
         <v>428</v>
       </c>
       <c r="AM27" t="s">
+        <v>473</v>
+      </c>
+      <c r="AN27" t="s">
         <v>474</v>
       </c>
-      <c r="AN27" t="s">
-        <v>382</v>
-      </c>
       <c r="AO27">
-        <v>0.99296304108660982</v>
+        <v>0.99637613831578808</v>
       </c>
       <c r="AP27">
-        <v>129.01091341215286</v>
+        <v>66.437464210551497</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9207,16 +9207,16 @@
         <v>325</v>
       </c>
       <c r="Y28" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Z28" t="s">
         <v>380</v>
       </c>
       <c r="AA28">
-        <v>0.99339354842512728</v>
+        <v>0.99133310355912085</v>
       </c>
       <c r="AB28">
-        <v>121.1182788726671</v>
+        <v>158.8931014161185</v>
       </c>
       <c r="AD28" t="s">
         <v>288</v>
@@ -9249,10 +9249,10 @@
         <v>476</v>
       </c>
       <c r="AO28">
-        <v>0.99562035686170025</v>
+        <v>0.9964390810242717</v>
       </c>
       <c r="AP28">
-        <v>80.293457535494625</v>
+        <v>65.283514555019096</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9317,16 +9317,16 @@
         <v>327</v>
       </c>
       <c r="Y29" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="Z29" t="s">
         <v>381</v>
       </c>
       <c r="AA29">
-        <v>0.99732710525923551</v>
+        <v>0.99601914721828588</v>
       </c>
       <c r="AB29">
-        <v>49.003070247349498</v>
+        <v>72.982300998092228</v>
       </c>
       <c r="AD29" t="s">
         <v>288</v>
@@ -9359,10 +9359,10 @@
         <v>478</v>
       </c>
       <c r="AO29">
-        <v>0.99740664776461363</v>
+        <v>0.99534990870245532</v>
       </c>
       <c r="AP29">
-        <v>47.544790982083583</v>
+        <v>85.251673788320105</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9427,16 +9427,16 @@
         <v>329</v>
       </c>
       <c r="Y30" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="Z30" t="s">
         <v>382</v>
       </c>
       <c r="AA30">
-        <v>0.99133310355912085</v>
+        <v>0.99383936956194807</v>
       </c>
       <c r="AB30">
-        <v>158.8931014161185</v>
+        <v>112.94489136428538</v>
       </c>
       <c r="AD30" t="s">
         <v>288</v>
@@ -9466,13 +9466,13 @@
         <v>479</v>
       </c>
       <c r="AN30" t="s">
-        <v>366</v>
+        <v>478</v>
       </c>
       <c r="AO30">
-        <v>0.99671794291781168</v>
+        <v>0.99555964959117016</v>
       </c>
       <c r="AP30">
-        <v>60.171046506785672</v>
+        <v>81.406424161880452</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9537,16 +9537,16 @@
         <v>331</v>
       </c>
       <c r="Y31" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="Z31" t="s">
         <v>383</v>
       </c>
       <c r="AA31">
-        <v>0.99601914721828588</v>
+        <v>0.99167897814293215</v>
       </c>
       <c r="AB31">
-        <v>72.982300998092228</v>
+        <v>152.55206737957732</v>
       </c>
       <c r="AD31" t="s">
         <v>288</v>
@@ -9576,13 +9576,13 @@
         <v>480</v>
       </c>
       <c r="AN31" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AO31">
-        <v>0.99008544123370779</v>
+        <v>0.99671794291781168</v>
       </c>
       <c r="AP31">
-        <v>181.76691071535706</v>
+        <v>60.171046506785672</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9647,16 +9647,16 @@
         <v>333</v>
       </c>
       <c r="Y32" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="Z32" t="s">
         <v>384</v>
       </c>
       <c r="AA32">
-        <v>0.99383936956194807</v>
+        <v>0.99750455285561002</v>
       </c>
       <c r="AB32">
-        <v>112.94489136428538</v>
+        <v>45.749864313816033</v>
       </c>
       <c r="AD32" t="s">
         <v>288</v>
@@ -9686,13 +9686,13 @@
         <v>481</v>
       </c>
       <c r="AN32" t="s">
-        <v>395</v>
+        <v>482</v>
       </c>
       <c r="AO32">
-        <v>0.99283555585293171</v>
+        <v>0.9913636988912532</v>
       </c>
       <c r="AP32">
-        <v>131.34814269625272</v>
+        <v>158.33218699369189</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9757,16 +9757,16 @@
         <v>335</v>
       </c>
       <c r="Y33" t="s">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="Z33" t="s">
         <v>385</v>
       </c>
       <c r="AA33">
-        <v>0.99631349511992195</v>
+        <v>0.99642867204968677</v>
       </c>
       <c r="AB33">
-        <v>67.585922801431252</v>
+        <v>65.474345755743457</v>
       </c>
       <c r="AD33" t="s">
         <v>288</v>
@@ -9793,16 +9793,16 @@
         <v>440</v>
       </c>
       <c r="AM33" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AN33" t="s">
-        <v>483</v>
+        <v>395</v>
       </c>
       <c r="AO33">
-        <v>0.99429686126958916</v>
+        <v>0.99698529931119073</v>
       </c>
       <c r="AP33">
-        <v>104.55754339086491</v>
+        <v>55.269512628170503</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -9867,16 +9867,16 @@
         <v>337</v>
       </c>
       <c r="Y34" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="Z34" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AA34">
-        <v>0.99514004796050048</v>
+        <v>0.99882431199806432</v>
       </c>
       <c r="AB34">
-        <v>89.099120724157018</v>
+        <v>21.554280035486567</v>
       </c>
       <c r="AD34" t="s">
         <v>288</v>
@@ -9909,10 +9909,10 @@
         <v>485</v>
       </c>
       <c r="AO34">
-        <v>0.99178855761800622</v>
+        <v>0.99501745221162918</v>
       </c>
       <c r="AP34">
-        <v>150.54311033655213</v>
+        <v>91.346709453464783</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -9977,16 +9977,16 @@
         <v>339</v>
       </c>
       <c r="Y35" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="Z35" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AA35">
-        <v>0.993124380119488</v>
+        <v>0.99629642371863703</v>
       </c>
       <c r="AB35">
-        <v>126.05303114271953</v>
+        <v>67.898898491655515</v>
       </c>
       <c r="AD35" t="s">
         <v>288</v>
@@ -10016,13 +10016,13 @@
         <v>486</v>
       </c>
       <c r="AN35" t="s">
-        <v>395</v>
+        <v>451</v>
       </c>
       <c r="AO35">
-        <v>0.99475386493829931</v>
+        <v>0.99582871194680656</v>
       </c>
       <c r="AP35">
-        <v>96.179142797845941</v>
+        <v>76.473614308545862</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -10087,16 +10087,16 @@
         <v>341</v>
       </c>
       <c r="Y36" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="Z36" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AA36">
-        <v>0.99884992726149324</v>
+        <v>0.99095032933880767</v>
       </c>
       <c r="AB36">
-        <v>21.084666872623977</v>
+        <v>165.91062878852651</v>
       </c>
       <c r="AD36" t="s">
         <v>288</v>
@@ -10126,13 +10126,13 @@
         <v>487</v>
       </c>
       <c r="AN36" t="s">
-        <v>488</v>
+        <v>380</v>
       </c>
       <c r="AO36">
-        <v>0.9913636988912532</v>
+        <v>0.99296304108660982</v>
       </c>
       <c r="AP36">
-        <v>158.33218699369189</v>
+        <v>129.01091341215286</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -10197,16 +10197,16 @@
         <v>343</v>
       </c>
       <c r="Y37" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="Z37" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AA37">
-        <v>0.99403967905190227</v>
+        <v>0.99631349511992195</v>
       </c>
       <c r="AB37">
-        <v>109.27255071512499</v>
+        <v>67.585922801431252</v>
       </c>
       <c r="AD37" t="s">
         <v>288</v>
@@ -10233,16 +10233,16 @@
         <v>448</v>
       </c>
       <c r="AM37" t="s">
+        <v>488</v>
+      </c>
+      <c r="AN37" t="s">
         <v>489</v>
       </c>
-      <c r="AN37" t="s">
-        <v>377</v>
-      </c>
       <c r="AO37">
-        <v>0.99698529931119073</v>
+        <v>0.99562035686170025</v>
       </c>
       <c r="AP37">
-        <v>55.269512628170503</v>
+        <v>80.293457535494625</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10307,16 +10307,16 @@
         <v>345</v>
       </c>
       <c r="Y38" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="Z38" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="AA38">
-        <v>0.99057172008573791</v>
+        <v>0.99514004796050048</v>
       </c>
       <c r="AB38">
-        <v>172.85179842813815</v>
+        <v>89.099120724157018</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -10381,16 +10381,16 @@
         <v>347</v>
       </c>
       <c r="Y39" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Z39" t="s">
         <v>390</v>
       </c>
       <c r="AA39">
-        <v>0.99644500818542014</v>
+        <v>0.993124380119488</v>
       </c>
       <c r="AB39">
-        <v>65.174849933963586</v>
+        <v>126.05303114271953</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -10455,16 +10455,16 @@
         <v>349</v>
       </c>
       <c r="Y40" t="s">
-        <v>284</v>
+        <v>259</v>
       </c>
       <c r="Z40" t="s">
         <v>391</v>
       </c>
       <c r="AA40">
-        <v>0.9963457067026108</v>
+        <v>0.99884992726149324</v>
       </c>
       <c r="AB40">
-        <v>66.99537711880258</v>
+        <v>21.084666872623977</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -10529,16 +10529,16 @@
         <v>351</v>
       </c>
       <c r="Y41" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Z41" t="s">
         <v>392</v>
       </c>
       <c r="AA41">
-        <v>0.99728758220200375</v>
+        <v>0.99403967905190227</v>
       </c>
       <c r="AB41">
-        <v>49.727659629930621</v>
+        <v>109.27255071512499</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -10603,16 +10603,16 @@
         <v>353</v>
       </c>
       <c r="Y42" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="Z42" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="AA42">
-        <v>0.99744993905722468</v>
+        <v>0.99057172008573791</v>
       </c>
       <c r="AB42">
-        <v>46.751117284213812</v>
+        <v>172.85179842813815</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -10677,16 +10677,16 @@
         <v>355</v>
       </c>
       <c r="Y43" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="Z43" t="s">
         <v>393</v>
       </c>
       <c r="AA43">
-        <v>0.99655017109874156</v>
+        <v>0.99802177249546054</v>
       </c>
       <c r="AB43">
-        <v>63.246863189739024</v>
+        <v>36.267504249889917</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -10751,16 +10751,16 @@
         <v>357</v>
       </c>
       <c r="Y44" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="Z44" t="s">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="AA44">
-        <v>0.99589467345586935</v>
+        <v>0.99769464806112851</v>
       </c>
       <c r="AB44">
-        <v>75.264319975727958</v>
+        <v>42.264785545976984</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -10825,16 +10825,16 @@
         <v>359</v>
       </c>
       <c r="Y45" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="Z45" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="AA45">
-        <v>0.99489048613238573</v>
+        <v>0.99605704806429607</v>
       </c>
       <c r="AB45">
-        <v>93.674420906261602</v>
+        <v>72.28745215457208</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -10899,16 +10899,16 @@
         <v>361</v>
       </c>
       <c r="Y46" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Z46" t="s">
         <v>395</v>
       </c>
       <c r="AA46">
-        <v>0.99436579068013853</v>
+        <v>0.99262439568706373</v>
       </c>
       <c r="AB46">
-        <v>103.29383753079337</v>
+        <v>135.21941240383219</v>
       </c>
     </row>
   </sheetData>
@@ -10917,7 +10917,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8648F55-D62D-4363-A143-6712FA039A4A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D9B614B-DEDC-4F74-AD5F-F133E9217050}">
   <dimension ref="B9:Z37"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11062,7 +11062,7 @@
         <v>575</v>
       </c>
       <c r="X11" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="Y11">
         <v>0.16350000000000001</v>
@@ -11130,7 +11130,7 @@
         <v>577</v>
       </c>
       <c r="X12" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="Y12">
         <v>13.40025</v>
@@ -11165,7 +11165,7 @@
         <v>525</v>
       </c>
       <c r="K13" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L13">
         <v>1.4400913107240583</v>
@@ -11198,7 +11198,7 @@
         <v>579</v>
       </c>
       <c r="X13" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="Y13">
         <v>8.4097500000000007</v>
@@ -11266,7 +11266,7 @@
         <v>581</v>
       </c>
       <c r="X14" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="Y14">
         <v>14.358750000000001</v>
@@ -11301,7 +11301,7 @@
         <v>529</v>
       </c>
       <c r="K15" t="s">
-        <v>475</v>
+        <v>488</v>
       </c>
       <c r="L15">
         <v>2.1922713563210485</v>
@@ -11334,7 +11334,7 @@
         <v>583</v>
       </c>
       <c r="X15" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="Y15">
         <v>12.78825</v>
@@ -11369,7 +11369,7 @@
         <v>531</v>
       </c>
       <c r="K16" t="s">
-        <v>482</v>
+        <v>464</v>
       </c>
       <c r="L16">
         <v>0.73811583011208182</v>
@@ -11437,7 +11437,7 @@
         <v>533</v>
       </c>
       <c r="K17" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="L17">
         <v>5.5236145427785717</v>
@@ -11470,7 +11470,7 @@
         <v>587</v>
       </c>
       <c r="X17" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="Y17">
         <v>8.6609999999999996</v>
@@ -11505,7 +11505,7 @@
         <v>535</v>
       </c>
       <c r="K18" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="L18">
         <v>5.5488357050452785E-3</v>
@@ -11538,7 +11538,7 @@
         <v>589</v>
       </c>
       <c r="X18" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="Y18">
         <v>3.4147500000000002</v>
@@ -11573,7 +11573,7 @@
         <v>537</v>
       </c>
       <c r="K19" t="s">
-        <v>454</v>
+        <v>475</v>
       </c>
       <c r="L19">
         <v>6.6811161360847313</v>
@@ -11674,7 +11674,7 @@
         <v>593</v>
       </c>
       <c r="X20" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="Y20">
         <v>6.8624999999999998</v>
@@ -11709,7 +11709,7 @@
         <v>541</v>
       </c>
       <c r="K21" t="s">
-        <v>484</v>
+        <v>466</v>
       </c>
       <c r="L21">
         <v>1.3529085560597105</v>
@@ -11744,7 +11744,7 @@
         <v>543</v>
       </c>
       <c r="K22" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="L22">
         <v>3.7088360788644938</v>
@@ -11779,7 +11779,7 @@
         <v>545</v>
       </c>
       <c r="K23" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="L23">
         <v>13.683903390107789</v>
@@ -11814,7 +11814,7 @@
         <v>547</v>
       </c>
       <c r="K24" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="L24">
         <v>5.4676081362262012</v>
@@ -11884,7 +11884,7 @@
         <v>551</v>
       </c>
       <c r="K26" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="L26">
         <v>14.189229081738485</v>
@@ -11919,7 +11919,7 @@
         <v>553</v>
       </c>
       <c r="K27" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="L27">
         <v>10.717982842540293</v>
@@ -11954,7 +11954,7 @@
         <v>555</v>
       </c>
       <c r="K28" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="L28">
         <v>9.6743476082482847</v>
@@ -11989,7 +11989,7 @@
         <v>557</v>
       </c>
       <c r="K29" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="L29">
         <v>23.206762484053751</v>
@@ -12024,7 +12024,7 @@
         <v>559</v>
       </c>
       <c r="K30" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="L30">
         <v>5.8372174437039801</v>
@@ -12059,7 +12059,7 @@
         <v>561</v>
       </c>
       <c r="K31" t="s">
-        <v>458</v>
+        <v>479</v>
       </c>
       <c r="L31">
         <v>1.8845590125315521</v>
@@ -12129,7 +12129,7 @@
         <v>565</v>
       </c>
       <c r="K33" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
       <c r="L33">
         <v>14.559476964149322</v>
@@ -12164,7 +12164,7 @@
         <v>567</v>
       </c>
       <c r="K34" t="s">
-        <v>464</v>
+        <v>484</v>
       </c>
       <c r="L34">
         <v>1.3536151515148049</v>
@@ -12199,7 +12199,7 @@
         <v>569</v>
       </c>
       <c r="K35" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="L35">
         <v>4.820514286595051</v>
@@ -12234,7 +12234,7 @@
         <v>571</v>
       </c>
       <c r="K36" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="L36">
         <v>8.1474073379531564</v>
@@ -12269,7 +12269,7 @@
         <v>573</v>
       </c>
       <c r="K37" t="s">
-        <v>456</v>
+        <v>477</v>
       </c>
       <c r="L37">
         <v>9.9689850956014183</v>
@@ -12284,7 +12284,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C93E06F9-7A9B-4EEB-864B-E23B376E46A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E0C4076-233D-41D7-B72C-2989D3D2DED8}">
   <dimension ref="B9:S128"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
